--- a/Bloque1/tema2/Libro1.xlsx
+++ b/Bloque1/tema2/Libro1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC225\Documents\GitHub\Base-de-datos-\Bloque1\tema2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4CA3BCE3-95C9-4785-A6FB-4960AB96CBB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB48FDDC-26FC-4BF3-8609-D612EC632F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{669E910F-652A-4F4E-9114-373B1D82A4B5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{669E910F-652A-4F4E-9114-373B1D82A4B5}"/>
   </bookViews>
   <sheets>
     <sheet name="JUGADORES" sheetId="1" r:id="rId1"/>
     <sheet name="CLUB " sheetId="2" r:id="rId2"/>
     <sheet name="ENTRENADORES" sheetId="3" r:id="rId3"/>
     <sheet name="PRESIDENTES" sheetId="4" r:id="rId4"/>
+    <sheet name="CIUDADES" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
   <si>
     <t>Jugador</t>
   </si>
@@ -140,18 +141,12 @@
     <t>Barcelona</t>
   </si>
   <si>
-    <t>Bilbao</t>
-  </si>
-  <si>
     <t>Vizcaya</t>
   </si>
   <si>
     <t>Valencia</t>
   </si>
   <si>
-    <t>París</t>
-  </si>
-  <si>
     <t>Francia</t>
   </si>
   <si>
@@ -198,13 +193,31 @@
   </si>
   <si>
     <t>Nasser Al-Khelaifi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciudad </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madrid </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barcelona </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valencia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilbao </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -221,6 +234,12 @@
     <font>
       <sz val="10"/>
       <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
@@ -272,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -283,6 +302,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -854,7 +877,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>3</v>
@@ -876,8 +899,8 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>30</v>
+      <c r="C2" s="2">
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>30</v>
@@ -893,8 +916,8 @@
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>31</v>
+      <c r="C3" s="3">
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>31</v>
@@ -910,8 +933,8 @@
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>30</v>
+      <c r="C4" s="2">
+        <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>30</v>
@@ -927,11 +950,11 @@
       <c r="B5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="3">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="E5" s="3">
         <v>1898</v>
@@ -944,11 +967,11 @@
       <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>34</v>
+      <c r="C6" s="2">
+        <v>4</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2">
         <v>1919</v>
@@ -961,11 +984,11 @@
       <c r="B7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>35</v>
+      <c r="C7" s="3">
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E7" s="3">
         <v>1970</v>
@@ -983,10 +1006,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -997,7 +1020,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -1008,7 +1031,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3">
         <v>2</v>
@@ -1019,7 +1042,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3">
         <v>3</v>
@@ -1030,7 +1053,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C5" s="3">
         <v>4</v>
@@ -1041,7 +1064,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3">
         <v>5</v>
@@ -1052,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C7" s="3">
         <v>6</v>
@@ -1070,10 +1093,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>3</v>
@@ -1083,8 +1106,8 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>46</v>
+      <c r="B2" s="4" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
@@ -1095,7 +1118,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3">
         <v>2</v>
@@ -1106,7 +1129,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -1117,7 +1140,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C5" s="3">
         <v>4</v>
@@ -1128,7 +1151,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2">
         <v>5</v>
@@ -1139,10 +1162,68 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3">
         <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99086AC9-F3FC-47E3-A446-51ED0ABC9275}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Bloque1/tema2/Libro1.xlsx
+++ b/Bloque1/tema2/Libro1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC225\Documents\GitHub\Base-de-datos-\Bloque1\tema2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB48FDDC-26FC-4BF3-8609-D612EC632F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{436E6A0D-C8C7-46E3-9F5B-50A1F94D7A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{669E910F-652A-4F4E-9114-373B1D82A4B5}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{669E910F-652A-4F4E-9114-373B1D82A4B5}"/>
   </bookViews>
   <sheets>
     <sheet name="JUGADORES" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="56">
   <si>
     <t>Jugador</t>
   </si>
@@ -264,7 +264,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -287,11 +287,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFD1D9E0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -306,6 +330,25 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,228 +683,462 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14E3CE7A-EE14-49EA-8F11-D9AD7553A922}">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="8">
         <v>9</v>
       </c>
-      <c r="E2" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="E2" s="8">
+        <v>1</v>
+      </c>
+      <c r="I2" s="6">
+        <v>1</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="8">
+        <v>1</v>
+      </c>
+      <c r="N2" s="6">
+        <v>1</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P2" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="3">
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="9">
         <v>7</v>
       </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="45.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="E3" s="9">
+        <v>1</v>
+      </c>
+      <c r="I3" s="6">
+        <v>2</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="9">
+        <v>1</v>
+      </c>
+      <c r="N3" s="6">
+        <v>2</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" ht="45" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2">
+      <c r="C4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="8">
         <v>9</v>
       </c>
-      <c r="E4" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="E4" s="8">
+        <v>2</v>
+      </c>
+      <c r="I4" s="6">
+        <v>3</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" s="8">
+        <v>2</v>
+      </c>
+      <c r="N4" s="6">
+        <v>3</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P4" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="9">
         <v>8</v>
       </c>
-      <c r="E5" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="E5" s="9">
+        <v>2</v>
+      </c>
+      <c r="I5" s="6">
+        <v>4</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" s="9">
+        <v>2</v>
+      </c>
+      <c r="N5" s="6">
+        <v>4</v>
+      </c>
+      <c r="O5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="2">
+      <c r="C6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="8">
         <v>7</v>
       </c>
-      <c r="E6" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="E6" s="8">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6">
+        <v>5</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="8">
+        <v>3</v>
+      </c>
+      <c r="N6" s="6">
+        <v>5</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P6" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="9">
         <v>13</v>
       </c>
-      <c r="E7" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="E7" s="9">
+        <v>3</v>
+      </c>
+      <c r="I7" s="6">
+        <v>6</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="K7" s="9">
+        <v>3</v>
+      </c>
+      <c r="N7" s="6">
+        <v>6</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="P7" s="9">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="2">
+      <c r="C8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="8">
         <v>10</v>
       </c>
-      <c r="E8" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="E8" s="8">
+        <v>4</v>
+      </c>
+      <c r="I8" s="6">
+        <v>7</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="8">
+        <v>4</v>
+      </c>
+      <c r="N8" s="6">
+        <v>7</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="3">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="D9" s="9">
+        <v>1</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4</v>
+      </c>
+      <c r="I9" s="6">
+        <v>8</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="9">
+        <v>4</v>
+      </c>
+      <c r="N9" s="6">
+        <v>8</v>
+      </c>
+      <c r="O9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="8">
         <v>14</v>
       </c>
-      <c r="E10" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="E10" s="8">
+        <v>5</v>
+      </c>
+      <c r="I10" s="6">
+        <v>9</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="8">
+        <v>5</v>
+      </c>
+      <c r="N10" s="6">
+        <v>9</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P10" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="3">
+      <c r="C11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="9">
         <v>9</v>
       </c>
-      <c r="E11" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="E11" s="9">
+        <v>5</v>
+      </c>
+      <c r="I11" s="6">
+        <v>10</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="9">
+        <v>5</v>
+      </c>
+      <c r="N11" s="6">
+        <v>10</v>
+      </c>
+      <c r="O11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="P11" s="9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="C12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8">
         <v>10</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="I12" s="6">
+        <v>11</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="8">
+        <v>6</v>
+      </c>
+      <c r="N12" s="6">
+        <v>11</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="30" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="3">
-        <v>2</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="D13" s="9">
+        <v>2</v>
+      </c>
+      <c r="E13" s="9">
         <v>6</v>
+      </c>
+      <c r="I13" s="6">
+        <v>12</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="9">
+        <v>6</v>
+      </c>
+      <c r="N13" s="6">
+        <v>12</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="P13" s="9">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -872,10 +1149,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{007A5444-E52C-430E-A386-7FB02B2BB23C}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>35</v>
       </c>
@@ -891,8 +1168,11 @@
       <c r="E1" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F1" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -908,8 +1188,11 @@
       <c r="E2" s="2">
         <v>1902</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F2" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -925,8 +1208,11 @@
       <c r="E3" s="3">
         <v>1899</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F3" s="12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -942,8 +1228,11 @@
       <c r="E4" s="2">
         <v>1903</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F4" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -959,8 +1248,11 @@
       <c r="E5" s="3">
         <v>1898</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F5" s="12">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -976,8 +1268,11 @@
       <c r="E6" s="2">
         <v>1919</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="F6" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -992,6 +1287,9 @@
       </c>
       <c r="E7" s="3">
         <v>1970</v>
+      </c>
+      <c r="F7" s="12">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
